--- a/artfynd/A 24641-2024 artfynd.xlsx
+++ b/artfynd/A 24641-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118433401</v>
+        <v>118434848</v>
       </c>
       <c r="B2" t="n">
-        <v>94620</v>
+        <v>91127</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>6031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ugglemossen (Ugglemossen), Sm</t>
+          <t>Flivikskärret (Flivikskärret), Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593554</v>
+        <v>593584</v>
       </c>
       <c r="R2" t="n">
-        <v>6380177</v>
+        <v>6380068</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118434848</v>
+        <v>118435675</v>
       </c>
       <c r="B3" t="n">
-        <v>91127</v>
+        <v>94620</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6031</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flivikskärret (Flivikskärret), Sm</t>
+          <t>Ugglemossen (Ugglemossen), Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593584</v>
+        <v>593452</v>
       </c>
       <c r="R3" t="n">
-        <v>6380068</v>
+        <v>6380169</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118435675</v>
+        <v>118433313</v>
       </c>
       <c r="B4" t="n">
-        <v>94620</v>
+        <v>90524</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593452</v>
+        <v>593572</v>
       </c>
       <c r="R4" t="n">
-        <v>6380169</v>
+        <v>6380190</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118433313</v>
+        <v>118433401</v>
       </c>
       <c r="B6" t="n">
-        <v>90524</v>
+        <v>94620</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,25 +1140,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593572</v>
+        <v>593554</v>
       </c>
       <c r="R6" t="n">
-        <v>6380190</v>
+        <v>6380177</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118453681</v>
+        <v>118451164</v>
       </c>
       <c r="B8" t="n">
-        <v>90524</v>
+        <v>94620</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,38 +1369,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ugglemossen (Ugglemossen), Sm</t>
+          <t>Flivikskärret (Flivikskärret), Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593586</v>
+        <v>593443</v>
       </c>
       <c r="R8" t="n">
-        <v>6380166</v>
+        <v>6380116</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118468262</v>
+        <v>118468392</v>
       </c>
       <c r="B9" t="n">
-        <v>94620</v>
+        <v>90718</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,31 +1481,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>1101</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1513,10 +1516,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593432</v>
+        <v>593539</v>
       </c>
       <c r="R9" t="n">
-        <v>6380125</v>
+        <v>6380123</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1549,6 +1552,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-07-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Fanns på en gammal granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118468302</v>
+        <v>118453681</v>
       </c>
       <c r="B10" t="n">
-        <v>57206</v>
+        <v>90524</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,49 +1600,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100067</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ugglemossen, Kallsebo, Sm</t>
+          <t>Ugglemossen (Ugglemossen), Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593419</v>
+        <v>593586</v>
       </c>
       <c r="R10" t="n">
-        <v>6380180</v>
+        <v>6380166</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1661,9 +1657,19 @@
           <t>2024-07-15</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-15</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,19 +1684,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118451164</v>
+        <v>118451213</v>
       </c>
       <c r="B11" t="n">
         <v>94620</v>
@@ -1723,20 +1729,29 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flivikskärret (Flivikskärret), Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593443</v>
+        <v>593419</v>
       </c>
       <c r="R11" t="n">
-        <v>6380116</v>
+        <v>6380094</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1765,7 +1780,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1775,7 +1790,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1802,10 +1817,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118468392</v>
+        <v>118468302</v>
       </c>
       <c r="B12" t="n">
-        <v>90718</v>
+        <v>57206</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1818,21 +1833,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1101</v>
+        <v>100067</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1840,8 +1855,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1849,10 +1869,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593539</v>
+        <v>593419</v>
       </c>
       <c r="R12" t="n">
-        <v>6380123</v>
+        <v>6380180</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1887,18 +1907,12 @@
           <t>2024-07-15</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Fanns på en gammal granlåga</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1917,7 +1931,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118451213</v>
+        <v>118468262</v>
       </c>
       <c r="B13" t="n">
         <v>94620</v>
@@ -1950,29 +1964,24 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Flivikskärret (Flivikskärret), Sm</t>
+          <t>Ugglemossen, Kallsebo, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593419</v>
+        <v>593432</v>
       </c>
       <c r="R13" t="n">
-        <v>6380094</v>
+        <v>6380125</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1999,49 +2008,40 @@
           <t>2024-07-15</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>08:34</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-07-15</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>08:34</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118486755</v>
+        <v>118473071</v>
       </c>
       <c r="B14" t="n">
-        <v>57309</v>
+        <v>100107</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2054,35 +2054,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102977</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2090,10 +2082,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593548</v>
+        <v>593522</v>
       </c>
       <c r="R14" t="n">
-        <v>6380230</v>
+        <v>6380219</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2134,6 +2126,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2152,10 +2145,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118473071</v>
+        <v>118486755</v>
       </c>
       <c r="B15" t="n">
-        <v>100107</v>
+        <v>57309</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2168,27 +2161,35 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>102977</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2196,10 +2197,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593522</v>
+        <v>593548</v>
       </c>
       <c r="R15" t="n">
-        <v>6380219</v>
+        <v>6380230</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2240,7 +2241,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24641-2024 artfynd.xlsx
+++ b/artfynd/A 24641-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118434848</v>
+        <v>118433401</v>
       </c>
       <c r="B2" t="n">
-        <v>91127</v>
+        <v>94620</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6031</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flivikskärret (Flivikskärret), Sm</t>
+          <t>Ugglemossen (Ugglemossen), Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593584</v>
+        <v>593554</v>
       </c>
       <c r="R2" t="n">
-        <v>6380068</v>
+        <v>6380177</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118435675</v>
+        <v>118434548</v>
       </c>
       <c r="B3" t="n">
-        <v>94620</v>
+        <v>57306</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +799,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ugglemossen (Ugglemossen), Sm</t>
+          <t>Flivikskärret (Flivikskärret), Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593452</v>
+        <v>593566</v>
       </c>
       <c r="R3" t="n">
-        <v>6380169</v>
+        <v>6380094</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118433313</v>
+        <v>118434848</v>
       </c>
       <c r="B4" t="n">
-        <v>90524</v>
+        <v>91127</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,38 +916,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ugglemossen (Ugglemossen), Sm</t>
+          <t>Flivikskärret (Flivikskärret), Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593572</v>
+        <v>593584</v>
       </c>
       <c r="R4" t="n">
-        <v>6380190</v>
+        <v>6380068</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118433329</v>
+        <v>118433313</v>
       </c>
       <c r="B5" t="n">
-        <v>57443</v>
+        <v>90524</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,42 +1032,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ugglemossen (Ugglemossen), Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593569</v>
+        <v>593572</v>
       </c>
       <c r="R5" t="n">
-        <v>6380179</v>
+        <v>6380190</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118433401</v>
+        <v>118435675</v>
       </c>
       <c r="B6" t="n">
         <v>94620</v>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593554</v>
+        <v>593452</v>
       </c>
       <c r="R6" t="n">
-        <v>6380177</v>
+        <v>6380169</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118434548</v>
+        <v>118433329</v>
       </c>
       <c r="B7" t="n">
-        <v>57306</v>
+        <v>57443</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,42 +1256,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Flivikskärret (Flivikskärret), Sm</t>
+          <t>Ugglemossen (Ugglemossen), Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593566</v>
+        <v>593569</v>
       </c>
       <c r="R7" t="n">
-        <v>6380094</v>
+        <v>6380179</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,7 +1357,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118451164</v>
+        <v>118451213</v>
       </c>
       <c r="B8" t="n">
         <v>94620</v>
@@ -1390,20 +1390,29 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flivikskärret (Flivikskärret), Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593443</v>
+        <v>593419</v>
       </c>
       <c r="R8" t="n">
-        <v>6380116</v>
+        <v>6380094</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1584,10 +1593,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118453681</v>
+        <v>118468262</v>
       </c>
       <c r="B10" t="n">
-        <v>90524</v>
+        <v>94620</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,41 +1605,45 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ugglemossen (Ugglemossen), Sm</t>
+          <t>Ugglemossen, Kallsebo, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593586</v>
+        <v>593432</v>
       </c>
       <c r="R10" t="n">
-        <v>6380166</v>
+        <v>6380125</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1657,49 +1670,40 @@
           <t>2024-07-15</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-15</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118451213</v>
+        <v>118468302</v>
       </c>
       <c r="B11" t="n">
-        <v>94620</v>
+        <v>57206</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1708,25 +1712,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>100067</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1734,24 +1738,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Flivikskärret (Flivikskärret), Sm</t>
+          <t>Ugglemossen, Kallsebo, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
         <v>593419</v>
       </c>
       <c r="R11" t="n">
-        <v>6380094</v>
+        <v>6380180</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1778,19 +1785,9 @@
           <t>2024-07-15</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>08:34</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-07-15</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>08:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,22 +1802,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118468302</v>
+        <v>118451164</v>
       </c>
       <c r="B12" t="n">
-        <v>57206</v>
+        <v>94620</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,53 +1826,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100067</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ugglemossen, Kallsebo, Sm</t>
+          <t>Flivikskärret (Flivikskärret), Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593419</v>
+        <v>593443</v>
       </c>
       <c r="R12" t="n">
-        <v>6380180</v>
+        <v>6380116</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1902,9 +1887,19 @@
           <t>2024-07-15</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-07-15</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1919,22 +1914,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118468262</v>
+        <v>118453681</v>
       </c>
       <c r="B13" t="n">
-        <v>94620</v>
+        <v>90524</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,45 +1938,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ugglemossen, Kallsebo, Sm</t>
+          <t>Ugglemossen (Ugglemossen), Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593432</v>
+        <v>593586</v>
       </c>
       <c r="R13" t="n">
-        <v>6380125</v>
+        <v>6380166</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2008,30 +1999,39 @@
           <t>2024-07-15</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-07-15</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118486755</v>
+        <v>118473076</v>
       </c>
       <c r="B15" t="n">
-        <v>57309</v>
+        <v>100107</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2161,35 +2161,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102977</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2235,12 +2227,18 @@
           <t>2024-07-15</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Riklig</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2259,10 +2257,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118473076</v>
+        <v>118486755</v>
       </c>
       <c r="B16" t="n">
-        <v>100107</v>
+        <v>57309</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2275,27 +2273,35 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>102977</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2341,18 +2347,12 @@
           <t>2024-07-15</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Riklig</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24641-2024 artfynd.xlsx
+++ b/artfynd/A 24641-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118433401</v>
+        <v>118434548</v>
       </c>
       <c r="B2" t="n">
-        <v>94620</v>
+        <v>57306</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ugglemossen (Ugglemossen), Sm</t>
+          <t>Flivikskärret (Flivikskärret), Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593554</v>
+        <v>593566</v>
       </c>
       <c r="R2" t="n">
-        <v>6380177</v>
+        <v>6380094</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118434548</v>
+        <v>118433401</v>
       </c>
       <c r="B3" t="n">
-        <v>57306</v>
+        <v>94627</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,43 +804,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flivikskärret (Flivikskärret), Sm</t>
+          <t>Ugglemossen (Ugglemossen), Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593566</v>
+        <v>593554</v>
       </c>
       <c r="R3" t="n">
-        <v>6380094</v>
+        <v>6380177</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118434848</v>
+        <v>118433329</v>
       </c>
       <c r="B4" t="n">
-        <v>91127</v>
+        <v>57443</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,41 +916,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6031</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Flivikskärret (Flivikskärret), Sm</t>
+          <t>Ugglemossen (Ugglemossen), Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593584</v>
+        <v>593569</v>
       </c>
       <c r="R4" t="n">
-        <v>6380068</v>
+        <v>6380179</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118433313</v>
+        <v>118435675</v>
       </c>
       <c r="B5" t="n">
-        <v>90524</v>
+        <v>94627</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,25 +1033,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593572</v>
+        <v>593452</v>
       </c>
       <c r="R5" t="n">
-        <v>6380190</v>
+        <v>6380169</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1091,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118435675</v>
+        <v>118434848</v>
       </c>
       <c r="B6" t="n">
-        <v>94620</v>
+        <v>91134</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,34 +1149,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>6031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ugglemossen (Ugglemossen), Sm</t>
+          <t>Flivikskärret (Flivikskärret), Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593452</v>
+        <v>593584</v>
       </c>
       <c r="R6" t="n">
-        <v>6380169</v>
+        <v>6380068</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1203,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118433329</v>
+        <v>118433313</v>
       </c>
       <c r="B7" t="n">
-        <v>57443</v>
+        <v>90531</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,42 +1261,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ugglemossen (Ugglemossen), Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593569</v>
+        <v>593572</v>
       </c>
       <c r="R7" t="n">
-        <v>6380179</v>
+        <v>6380190</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118451213</v>
+        <v>118468392</v>
       </c>
       <c r="B8" t="n">
-        <v>94620</v>
+        <v>90725</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,25 +1369,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>1101</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1395,24 +1395,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Flivikskärret (Flivikskärret), Sm</t>
+          <t>Ugglemossen, Kallsebo, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593419</v>
+        <v>593539</v>
       </c>
       <c r="R8" t="n">
-        <v>6380094</v>
+        <v>6380123</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1439,19 +1437,14 @@
           <t>2024-07-15</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>08:34</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-15</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>08:34</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Fanns på en gammal granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1460,28 +1453,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118468392</v>
+        <v>118451213</v>
       </c>
       <c r="B9" t="n">
-        <v>90718</v>
+        <v>94627</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,25 +1484,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1101</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1516,22 +1510,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ugglemossen, Kallsebo, Sm</t>
+          <t>Flivikskärret (Flivikskärret), Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593539</v>
+        <v>593419</v>
       </c>
       <c r="R9" t="n">
-        <v>6380123</v>
+        <v>6380094</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1558,14 +1554,19 @@
           <t>2024-07-15</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-07-15</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Fanns på en gammal granlåga</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,29 +1575,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118468262</v>
+        <v>118451164</v>
       </c>
       <c r="B10" t="n">
-        <v>94620</v>
+        <v>94627</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,23 +1627,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ugglemossen, Kallsebo, Sm</t>
+          <t>Flivikskärret (Flivikskärret), Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593432</v>
+        <v>593443</v>
       </c>
       <c r="R10" t="n">
-        <v>6380125</v>
+        <v>6380116</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1670,40 +1666,49 @@
           <t>2024-07-15</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-15</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118468302</v>
+        <v>118468262</v>
       </c>
       <c r="B11" t="n">
-        <v>57206</v>
+        <v>94627</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1712,39 +1717,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100067</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1752,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593419</v>
+        <v>593432</v>
       </c>
       <c r="R11" t="n">
-        <v>6380180</v>
+        <v>6380125</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1796,6 +1793,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1814,10 +1812,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118451164</v>
+        <v>118453681</v>
       </c>
       <c r="B12" t="n">
-        <v>94620</v>
+        <v>90531</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,38 +1824,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Flivikskärret (Flivikskärret), Sm</t>
+          <t>Ugglemossen (Ugglemossen), Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593443</v>
+        <v>593586</v>
       </c>
       <c r="R12" t="n">
-        <v>6380116</v>
+        <v>6380166</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1889,7 +1887,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1899,7 +1897,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,10 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118453681</v>
+        <v>118468302</v>
       </c>
       <c r="B13" t="n">
-        <v>90524</v>
+        <v>57206</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,37 +1940,49 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>100067</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ugglemossen (Ugglemossen), Sm</t>
+          <t>Ugglemossen, Kallsebo, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593586</v>
+        <v>593419</v>
       </c>
       <c r="R13" t="n">
-        <v>6380166</v>
+        <v>6380180</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1999,19 +2009,9 @@
           <t>2024-07-15</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-07-15</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2026,22 +2026,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118473071</v>
+        <v>118473076</v>
       </c>
       <c r="B14" t="n">
-        <v>100107</v>
+        <v>100114</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2082,10 +2082,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593522</v>
+        <v>593548</v>
       </c>
       <c r="R14" t="n">
-        <v>6380219</v>
+        <v>6380230</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2118,6 +2118,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-07-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2145,10 +2150,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118473076</v>
+        <v>118473071</v>
       </c>
       <c r="B15" t="n">
-        <v>100107</v>
+        <v>100114</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2189,10 +2194,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593548</v>
+        <v>593522</v>
       </c>
       <c r="R15" t="n">
-        <v>6380230</v>
+        <v>6380219</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2225,11 +2230,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-07-15</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Riklig</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2257,10 +2257,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118486755</v>
+        <v>118472957</v>
       </c>
       <c r="B16" t="n">
-        <v>57309</v>
+        <v>90531</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2269,25 +2269,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102977</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2295,13 +2295,8 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2309,10 +2304,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593548</v>
+        <v>593575</v>
       </c>
       <c r="R16" t="n">
-        <v>6380230</v>
+        <v>6380193</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2353,6 +2348,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2371,10 +2367,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118472957</v>
+        <v>118486755</v>
       </c>
       <c r="B17" t="n">
-        <v>90524</v>
+        <v>57309</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2383,25 +2379,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>102977</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2409,8 +2405,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2418,10 +2419,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593575</v>
+        <v>593548</v>
       </c>
       <c r="R17" t="n">
-        <v>6380193</v>
+        <v>6380230</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2462,7 +2463,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2484,7 +2484,7 @@
         <v>118468242</v>
       </c>
       <c r="B18" t="n">
-        <v>94620</v>
+        <v>94627</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 24641-2024 artfynd.xlsx
+++ b/artfynd/A 24641-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118434548</v>
+        <v>118433313</v>
       </c>
       <c r="B2" t="n">
-        <v>57306</v>
+        <v>90531</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flivikskärret (Flivikskärret), Sm</t>
+          <t>Ugglemossen (Ugglemossen), Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593566</v>
+        <v>593572</v>
       </c>
       <c r="R2" t="n">
-        <v>6380094</v>
+        <v>6380190</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118433329</v>
+        <v>118434848</v>
       </c>
       <c r="B4" t="n">
-        <v>57443</v>
+        <v>91134</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,46 +911,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ugglemossen (Ugglemossen), Sm</t>
+          <t>Flivikskärret (Flivikskärret), Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593569</v>
+        <v>593584</v>
       </c>
       <c r="R4" t="n">
-        <v>6380179</v>
+        <v>6380068</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1133,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118434848</v>
+        <v>118433329</v>
       </c>
       <c r="B6" t="n">
-        <v>91134</v>
+        <v>57443</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,41 +1135,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6031</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Flivikskärret (Flivikskärret), Sm</t>
+          <t>Ugglemossen (Ugglemossen), Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593584</v>
+        <v>593569</v>
       </c>
       <c r="R6" t="n">
-        <v>6380068</v>
+        <v>6380179</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118433313</v>
+        <v>118434548</v>
       </c>
       <c r="B7" t="n">
-        <v>90531</v>
+        <v>57306</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,34 +1256,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ugglemossen (Ugglemossen), Sm</t>
+          <t>Flivikskärret (Flivikskärret), Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593572</v>
+        <v>593566</v>
       </c>
       <c r="R7" t="n">
-        <v>6380190</v>
+        <v>6380094</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118468392</v>
+        <v>118451164</v>
       </c>
       <c r="B8" t="n">
-        <v>90725</v>
+        <v>94627</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,48 +1369,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1101</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ugglemossen, Kallsebo, Sm</t>
+          <t>Flivikskärret (Flivikskärret), Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593539</v>
+        <v>593443</v>
       </c>
       <c r="R8" t="n">
-        <v>6380123</v>
+        <v>6380116</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1437,14 +1430,19 @@
           <t>2024-07-15</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-15</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Fanns på en gammal granlåga</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,29 +1451,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118451213</v>
+        <v>118468392</v>
       </c>
       <c r="B9" t="n">
-        <v>94627</v>
+        <v>90725</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,25 +1481,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>1101</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1510,24 +1507,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Flivikskärret (Flivikskärret), Sm</t>
+          <t>Ugglemossen, Kallsebo, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593419</v>
+        <v>593539</v>
       </c>
       <c r="R9" t="n">
-        <v>6380094</v>
+        <v>6380123</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1554,19 +1549,14 @@
           <t>2024-07-15</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>08:34</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-07-15</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>08:34</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Fanns på en gammal granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,28 +1565,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118451164</v>
+        <v>118468302</v>
       </c>
       <c r="B10" t="n">
-        <v>94627</v>
+        <v>57206</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,41 +1596,53 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>100067</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Flivikskärret (Flivikskärret), Sm</t>
+          <t>Ugglemossen, Kallsebo, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593443</v>
+        <v>593419</v>
       </c>
       <c r="R10" t="n">
-        <v>6380116</v>
+        <v>6380180</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1666,19 +1669,9 @@
           <t>2024-07-15</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>08:29</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-15</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>08:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,19 +1686,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118468262</v>
+        <v>118451213</v>
       </c>
       <c r="B11" t="n">
         <v>94627</v>
@@ -1738,24 +1731,29 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ugglemossen, Kallsebo, Sm</t>
+          <t>Flivikskärret (Flivikskärret), Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593432</v>
+        <v>593419</v>
       </c>
       <c r="R11" t="n">
-        <v>6380125</v>
+        <v>6380094</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1782,40 +1780,49 @@
           <t>2024-07-15</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-07-15</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118453681</v>
+        <v>118468262</v>
       </c>
       <c r="B12" t="n">
-        <v>90531</v>
+        <v>94627</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1824,41 +1831,45 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ugglemossen (Ugglemossen), Sm</t>
+          <t>Ugglemossen, Kallsebo, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593586</v>
+        <v>593432</v>
       </c>
       <c r="R12" t="n">
-        <v>6380166</v>
+        <v>6380125</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1885,49 +1896,40 @@
           <t>2024-07-15</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-07-15</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118468302</v>
+        <v>118453681</v>
       </c>
       <c r="B13" t="n">
-        <v>57206</v>
+        <v>90531</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1940,49 +1942,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100067</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ugglemossen, Kallsebo, Sm</t>
+          <t>Ugglemossen (Ugglemossen), Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593419</v>
+        <v>593586</v>
       </c>
       <c r="R13" t="n">
-        <v>6380180</v>
+        <v>6380166</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2009,9 +1999,19 @@
           <t>2024-07-15</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-07-15</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2026,12 +2026,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2150,10 +2150,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118473071</v>
+        <v>118472957</v>
       </c>
       <c r="B15" t="n">
-        <v>100114</v>
+        <v>90531</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,31 +2162,34 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2194,10 +2197,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593522</v>
+        <v>593575</v>
       </c>
       <c r="R15" t="n">
-        <v>6380219</v>
+        <v>6380193</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2257,10 +2260,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118472957</v>
+        <v>118486755</v>
       </c>
       <c r="B16" t="n">
-        <v>90531</v>
+        <v>57309</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2269,25 +2272,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>102977</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2295,8 +2298,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2304,10 +2312,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593575</v>
+        <v>593548</v>
       </c>
       <c r="R16" t="n">
-        <v>6380193</v>
+        <v>6380230</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2348,7 +2356,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2367,10 +2374,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118486755</v>
+        <v>118473071</v>
       </c>
       <c r="B17" t="n">
-        <v>57309</v>
+        <v>100114</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2383,35 +2390,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102977</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2419,10 +2418,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593548</v>
+        <v>593522</v>
       </c>
       <c r="R17" t="n">
-        <v>6380230</v>
+        <v>6380219</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2463,6 +2462,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24641-2024 artfynd.xlsx
+++ b/artfynd/A 24641-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118433329</v>
+        <v>118468392</v>
       </c>
       <c r="B2" t="n">
-        <v>57445</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +686,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>1101</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ugglemossen (Ugglemossen), Sm</t>
+          <t>Ugglemossen, Kallsebo, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593569</v>
+        <v>593539</v>
       </c>
       <c r="R2" t="n">
-        <v>6380179</v>
+        <v>6380123</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +747,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:07</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:07</t>
+          <t>2024-07-15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Fanns på en gammal granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,33 +766,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118434848</v>
+        <v>118433401</v>
       </c>
       <c r="B3" t="n">
-        <v>91136</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,34 +796,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6031</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flivikskärret (Flivikskärret), Sm</t>
+          <t>Ugglemossen, Ugglemossen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593584</v>
+        <v>593554</v>
       </c>
       <c r="R3" t="n">
-        <v>6380068</v>
+        <v>6380177</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -867,7 +855,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +865,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,55 +892,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118434548</v>
+        <v>118435675</v>
       </c>
       <c r="B4" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Flivikskärret (Flivikskärret), Sm</t>
+          <t>Ugglemossen, Ugglemossen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593566</v>
+        <v>593452</v>
       </c>
       <c r="R4" t="n">
-        <v>6380094</v>
+        <v>6380169</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -984,7 +962,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +972,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,50 +999,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118433313</v>
+        <v>118451164</v>
       </c>
       <c r="B5" t="n">
-        <v>90533</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ugglemossen (Ugglemossen), Sm</t>
+          <t>Flivikskärret, Flivikskärret, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593572</v>
+        <v>593443</v>
       </c>
       <c r="R5" t="n">
-        <v>6380190</v>
+        <v>6380116</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1091,22 +1064,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,15 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118433401</v>
+        <v>118451213</v>
       </c>
       <c r="B6" t="n">
-        <v>94629</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1166,20 +1134,29 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ugglemossen (Ugglemossen), Sm</t>
+          <t>Flivikskärret, Flivikskärret, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593554</v>
+        <v>593419</v>
       </c>
       <c r="R6" t="n">
-        <v>6380177</v>
+        <v>6380094</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,22 +1180,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,15 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118435675</v>
+        <v>118468242</v>
       </c>
       <c r="B7" t="n">
-        <v>94629</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,19 +1251,23 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ugglemossen (Ugglemossen), Sm</t>
+          <t>Ugglemossen, Kallsebo, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593452</v>
+        <v>593457</v>
       </c>
       <c r="R7" t="n">
-        <v>6380169</v>
+        <v>6380172</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,22 +1291,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:44</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:44</t>
+          <t>2024-07-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Riklig på bergshällar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,64 +1310,57 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118468392</v>
+        <v>118468262</v>
       </c>
       <c r="B8" t="n">
-        <v>90727</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1101</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1404,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593539</v>
+        <v>593432</v>
       </c>
       <c r="R8" t="n">
-        <v>6380123</v>
+        <v>6380125</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1440,11 +1404,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Fanns på en gammal granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,51 +1431,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118468302</v>
+        <v>118473048</v>
       </c>
       <c r="B9" t="n">
-        <v>57208</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100067</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1524,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593419</v>
+        <v>593432</v>
       </c>
       <c r="R9" t="n">
-        <v>6380180</v>
+        <v>6380264</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1562,12 +1508,18 @@
           <t>2024-07-15</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Riklig förekomst på brghällar</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1586,50 +1538,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118451164</v>
+        <v>118433313</v>
       </c>
       <c r="B10" t="n">
-        <v>94629</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Flivikskärret (Flivikskärret), Sm</t>
+          <t>Ugglemossen, Ugglemossen, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593443</v>
+        <v>593572</v>
       </c>
       <c r="R10" t="n">
-        <v>6380116</v>
+        <v>6380190</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1656,22 +1603,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,12 +1648,7 @@
         <v>118453681</v>
       </c>
       <c r="B11" t="n">
-        <v>90533</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1734,7 +1676,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ugglemossen (Ugglemossen), Sm</t>
+          <t>Ugglemossen, Ugglemossen, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -1810,43 +1752,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118468262</v>
+        <v>118472957</v>
       </c>
       <c r="B12" t="n">
-        <v>94629</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1854,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593432</v>
+        <v>593575</v>
       </c>
       <c r="R12" t="n">
-        <v>6380125</v>
+        <v>6380193</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1917,37 +1857,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118451213</v>
+        <v>118472995</v>
       </c>
       <c r="B13" t="n">
-        <v>94629</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1955,24 +1890,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Flivikskärret (Flivikskärret), Sm</t>
+          <t>Ugglemossen, Kallsebo, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593419</v>
+        <v>593408</v>
       </c>
       <c r="R13" t="n">
-        <v>6380094</v>
+        <v>6380296</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1999,54 +1932,40 @@
           <t>2024-07-15</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>08:34</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-07-15</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>08:34</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118473071</v>
+        <v>118434848</v>
       </c>
       <c r="B14" t="n">
-        <v>100116</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,41 +1973,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>6031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ugglemossen, Kallsebo, Sm</t>
+          <t>Flivikskärret, Flivikskärret, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593522</v>
+        <v>593584</v>
       </c>
       <c r="R14" t="n">
-        <v>6380219</v>
+        <v>6380068</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2112,12 +2027,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2126,34 +2051,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118473076</v>
+        <v>118434548</v>
       </c>
       <c r="B15" t="n">
-        <v>100116</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,41 +2080,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ugglemossen, Kallsebo, Sm</t>
+          <t>Flivikskärret, Flivikskärret, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593548</v>
+        <v>593566</v>
       </c>
       <c r="R15" t="n">
-        <v>6380230</v>
+        <v>6380094</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2219,17 +2139,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Riklig</t>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2238,34 +2163,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118486755</v>
+        <v>118468302</v>
       </c>
       <c r="B16" t="n">
-        <v>57311</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,21 +2192,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102977</v>
+        <v>100067</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2309,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593548</v>
+        <v>593419</v>
       </c>
       <c r="R16" t="n">
-        <v>6380230</v>
+        <v>6380180</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2371,37 +2290,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118472957</v>
+        <v>118473032</v>
       </c>
       <c r="B17" t="n">
-        <v>90533</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>102977</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2409,8 +2323,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2418,10 +2337,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593575</v>
+        <v>593408</v>
       </c>
       <c r="R17" t="n">
-        <v>6380193</v>
+        <v>6380296</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2462,7 +2381,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2481,15 +2399,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118468242</v>
+        <v>118486755</v>
       </c>
       <c r="B18" t="n">
-        <v>94632</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,27 +2410,35 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>102977</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2525,10 +2446,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593457</v>
+        <v>593548</v>
       </c>
       <c r="R18" t="n">
-        <v>6380172</v>
+        <v>6380230</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2563,18 +2484,12 @@
           <t>2024-07-15</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Riklig på bergshällar</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2590,6 +2505,439 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>118432980</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ugglemossen, Ugglemossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>593463</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6380259</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>118433329</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ugglemossen, Ugglemossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>593569</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6380179</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>118473071</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ugglemossen, Kallsebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>593522</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6380219</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-07-15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-07-15</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>118473076</v>
+      </c>
+      <c r="B22" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ugglemossen, Kallsebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>593548</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6380230</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-07-15</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-07-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Riklig</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24641-2024 artfynd.xlsx
+++ b/artfynd/A 24641-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118468392</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118433401</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118435675</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,6 +1123,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118451164</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1219,6 +1244,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118451213</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1326,6 +1356,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118468242</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1428,6 +1463,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118468262</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1535,6 +1575,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118473048</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1642,6 +1687,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118433313</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1749,6 +1799,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118453681</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1854,6 +1909,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118472957</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1959,6 +2019,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118472995</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2066,6 +2131,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118434848</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2178,6 +2248,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118434548</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2287,6 +2362,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118468302</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2396,6 +2476,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118473032</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2505,6 +2590,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118486755</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2617,6 +2707,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118432980</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2729,6 +2824,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118433329</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2831,6 +2931,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118473071</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2938,8 +3043,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118473076</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>